--- a/templates/office/EMP_MAN_030_이슈관리대장.xlsx
+++ b/templates/office/EMP_MAN_030_이슈관리대장.xlsx
@@ -1446,7 +1446,7 @@
       </c>
       <c r="C16" s="106" t="inlineStr">
         <is>
-          <t>아모레퍼시픽 SyncGuard AI 시스템 구축</t>
+          <t>한빛글로벌 SyncGuard AI 시스템 구축</t>
         </is>
       </c>
       <c r="D16" s="115" t="n"/>
@@ -1497,12 +1497,12 @@
     <row r="22">
       <c r="C22" t="inlineStr">
         <is>
-          <t>그로브소프트 (EMPASY)</t>
+          <t>엠파시 (EMPASY)</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>아모레퍼시픽</t>
+          <t>한빛글로벌</t>
         </is>
       </c>
     </row>
@@ -1510,7 +1510,7 @@
     <row r="26" ht="22.15" customFormat="1" customHeight="1" s="7">
       <c r="C26" s="118" t="inlineStr">
         <is>
-          <t>그로브소프트</t>
+          <t>엠파시</t>
         </is>
       </c>
       <c r="D26" s="119" t="n"/>
@@ -1672,12 +1672,12 @@
       </c>
       <c r="C4" s="128" t="inlineStr">
         <is>
-          <t>사내 기간계(티움넷·마이비커·SSO) 연계 규격 협의</t>
+          <t>사내 기간계(마케팅허브·프로덕트랩·SSO) 연계 규격 협의</t>
         </is>
       </c>
       <c r="D4" s="129" t="inlineStr">
         <is>
-          <t>현업 주 접점인 티움넷 의뢰/결과 연동 및 마이비커 전성분·실증 DB 조회 인터페이스 상세 규격 조기 확정 필요</t>
+          <t>현업 주 접점인 마케팅허브 의뢰/결과 연동 및 프로덕트랩 전성분·실증 DB 조회 인터페이스 상세 규격 조기 확정 필요</t>
         </is>
       </c>
       <c r="E4" s="130" t="inlineStr">
@@ -1702,7 +1702,7 @@
       </c>
       <c r="I4" s="131" t="inlineStr">
         <is>
-          <t>김재은 PM / 아이시프트</t>
+          <t>김태윤 PM / 데이터브릿지</t>
         </is>
       </c>
       <c r="J4" s="25" t="inlineStr">
@@ -1754,7 +1754,7 @@
       </c>
       <c r="I5" s="131" t="inlineStr">
         <is>
-          <t>오병문 AA</t>
+          <t>박준혁 AA</t>
         </is>
       </c>
       <c r="J5" s="26" t="inlineStr">
@@ -1806,7 +1806,7 @@
       </c>
       <c r="I6" s="132" t="inlineStr">
         <is>
-          <t>오병문 AA</t>
+          <t>박준혁 AA</t>
         </is>
       </c>
       <c r="J6" s="26" t="inlineStr">
@@ -1858,7 +1858,7 @@
       </c>
       <c r="I7" s="131" t="inlineStr">
         <is>
-          <t>오병문 AA / 장지용 PL</t>
+          <t>박준혁 AA / 최현우 PL</t>
         </is>
       </c>
       <c r="J7" s="26" t="inlineStr">
@@ -1910,7 +1910,7 @@
       </c>
       <c r="I8" s="131" t="inlineStr">
         <is>
-          <t>김재은 PM / RA Lab</t>
+          <t>김태윤 PM / RA Lab</t>
         </is>
       </c>
       <c r="J8" s="26" t="inlineStr">
@@ -1962,7 +1962,7 @@
       </c>
       <c r="I9" s="137" t="inlineStr">
         <is>
-          <t>김재은 PM / 박주열 PM</t>
+          <t>김태윤 PM / 정민수 PM</t>
         </is>
       </c>
       <c r="J9" s="59" t="inlineStr">
@@ -2014,7 +2014,7 @@
       </c>
       <c r="I10" s="137" t="inlineStr">
         <is>
-          <t>오병문 AA</t>
+          <t>박준혁 AA</t>
         </is>
       </c>
       <c r="J10" s="60" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="I11" s="137" t="inlineStr">
         <is>
-          <t>오병문 AA</t>
+          <t>박준혁 AA</t>
         </is>
       </c>
       <c r="J11" s="60" t="inlineStr">
@@ -2118,7 +2118,7 @@
       </c>
       <c r="I12" s="137" t="inlineStr">
         <is>
-          <t>오병문 AA</t>
+          <t>박준혁 AA</t>
         </is>
       </c>
       <c r="J12" s="60" t="inlineStr">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="I13" s="137" t="inlineStr">
         <is>
-          <t>장지용 PL</t>
+          <t>최현우 PL</t>
         </is>
       </c>
       <c r="J13" s="60" t="inlineStr">

--- a/templates/office/EMP_MAN_030_이슈관리대장.xlsx
+++ b/templates/office/EMP_MAN_030_이슈관리대장.xlsx
@@ -1446,7 +1446,7 @@
       </c>
       <c r="C16" s="106" t="inlineStr">
         <is>
-          <t>한빛글로벌 SyncGuard AI 시스템 구축</t>
+          <t>한빛글로벌 SyncFlow AI 시스템 구축</t>
         </is>
       </c>
       <c r="D16" s="115" t="n"/>
@@ -1516,7 +1516,7 @@
       <c r="D26" s="119" t="n"/>
       <c r="E26" s="120" t="inlineStr">
         <is>
-          <t>고객사명</t>
+          <t>주식회사 한빛글로벌</t>
         </is>
       </c>
       <c r="F26" s="121" t="n"/>
@@ -1672,12 +1672,12 @@
       </c>
       <c r="C4" s="128" t="inlineStr">
         <is>
-          <t>사내 기간계(마케팅허브·프로덕트랩·SSO) 연계 규격 협의</t>
+          <t>사내 기간계(전자구매포털·피엘엠넥서스·SSO) 연계 규격 협의</t>
         </is>
       </c>
       <c r="D4" s="129" t="inlineStr">
         <is>
-          <t>현업 주 접점인 마케팅허브 의뢰/결과 연동 및 프로덕트랩 전성분·실증 DB 조회 인터페이스 상세 규격 조기 확정 필요</t>
+          <t>현업 주 접점인 전자구매포털 의뢰/결과 연동 및 피엘엠넥서스 자재BOM·시험검증 DB 조회 인터페이스 상세 규격 조기 확정 필요</t>
         </is>
       </c>
       <c r="E4" s="130" t="inlineStr">
@@ -1724,12 +1724,12 @@
       </c>
       <c r="C5" s="128" t="inlineStr">
         <is>
-          <t>동영상(쇼츠·롱폼) 심의 방식 및 리소스 최적화</t>
+          <t>설계도면(도면시트·롱폼) 검증 방식 및 리소스 최적화</t>
         </is>
       </c>
       <c r="D5" s="128" t="inlineStr">
         <is>
-          <t>흘러가는 영상을 무작위 자동 캡처할 경우 글자 전환 중 겹침 오인식이 발생하고 롱폼 전체 분석 시 리소스 과다 소요</t>
+          <t>흘러가는 영상을 무작위 자동 스냅샷할 경우 글자 전환 중 겹침 오인식이 발생하고 롱폼 전체 분석 시 리소스 과다 소요</t>
         </is>
       </c>
       <c r="E5" s="130" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="G5" s="127" t="inlineStr">
         <is>
-          <t>동영상 장면 캡처</t>
+          <t>설계도면 스냅샷 추출</t>
         </is>
       </c>
       <c r="H5" s="127" t="inlineStr">
@@ -1759,7 +1759,7 @@
       </c>
       <c r="J5" s="26" t="inlineStr">
         <is>
-          <t>사용자가 영상 재생 중 심의할 여러 장면을 직접 지정·캡처하여 이미지로 저장 후 일괄 심의하는 PoC 검증 완료(10/23)</t>
+          <t>사용자가 영상 재생 중 검증할 여러 장면을 직접 지정·스냅샷하여 이미지로 저장 후 일괄 검증하는 PoC 검증 완료(10/23)</t>
         </is>
       </c>
     </row>
@@ -1776,12 +1776,12 @@
       </c>
       <c r="C6" s="128" t="inlineStr">
         <is>
-          <t>[Option] KT 레몬 vs 상용 LLM 보고서 파싱 품질 비교</t>
+          <t>[Option] HB-Monitor vs 상용 LLM 보고서 파싱 품질 비교</t>
         </is>
       </c>
       <c r="D6" s="128" t="inlineStr">
         <is>
-          <t>R&amp;I 연구보고서 벡터 데이터(KT 레몬) API 호출 방식과 상용 LLM(Claude 등) 원문 직접 파싱 간 정확도 사전 비교 필요</t>
+          <t>선행연구소 연구보고서 벡터 데이터(HB-Monitor) API 호출 방식과 상용 LLM(Claude 등) 원문 직접 파싱 간 정확도 사전 비교 필요</t>
         </is>
       </c>
       <c r="E6" s="130" t="inlineStr">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="G6" s="127" t="inlineStr">
         <is>
-          <t>RAG / 실증연계</t>
+          <t>RAG / 시험검증연계</t>
         </is>
       </c>
       <c r="H6" s="127" t="inlineStr">
@@ -1811,7 +1811,7 @@
       </c>
       <c r="J6" s="26" t="inlineStr">
         <is>
-          <t>아키텍처 내 KT 레몬을 [Option] 플러그인 구조로 분리 설계하고 11월 중 샘플 보고서 비교 테스트 후 확정</t>
+          <t>아키텍처 내 HB-Monitor을 [Option] 플러그인 구조로 분리 설계하고 11월 중 샘플 보고서 비교 테스트 후 확정</t>
         </is>
       </c>
     </row>
@@ -1880,12 +1880,12 @@
       </c>
       <c r="C8" s="128" t="inlineStr">
         <is>
-          <t>식약처 가이드라인 및 골든셋 참조 데이터(50건) 수령</t>
+          <t>공정위·표준원 가이드라인 및 골든셋 참조 데이터(50건) 수령</t>
         </is>
       </c>
       <c r="D8" s="129" t="inlineStr">
         <is>
-          <t>초기 표현 사전 구축 및 AI 판정 정밀도 기준 측정을 위한 현업 심의 스크립트·가이드라인 단일 포맷 수령 필요</t>
+          <t>초기 표현 사전 구축 및 AI 판정 정밀도 기준 측정을 위한 현업 검증 스크립트·가이드라인 단일 포맷 수령 필요</t>
         </is>
       </c>
       <c r="E8" s="130" t="inlineStr">
@@ -1910,7 +1910,7 @@
       </c>
       <c r="I8" s="131" t="inlineStr">
         <is>
-          <t>김태윤 PM / RA Lab</t>
+          <t>김태윤 PM / 품질법무검증팀</t>
         </is>
       </c>
       <c r="J8" s="26" t="inlineStr">
@@ -1932,12 +1932,12 @@
       </c>
       <c r="C9" s="134" t="inlineStr">
         <is>
-          <t>국·영문 혼용 시안 번역 심의 및 과업 제외 경계 명확화</t>
+          <t>국·영문 혼용 계약·도서 번역 검증 및 과업 제외 경계 명확화</t>
         </is>
       </c>
       <c r="D9" s="135" t="inlineStr">
         <is>
-          <t>시안 내 영문 소구 문구 심의 포함 여부 및 인물 얼굴/딥페이크·해외 법률 심의 제외 기준 명확화 필요</t>
+          <t>계약·도서 내 영문 기술사양 조항 검증 포함 여부 및 3D 솔리드 모델링·해외 법률 검증 제외 기준 명확화 필요</t>
         </is>
       </c>
       <c r="E9" s="136" t="inlineStr">
@@ -1967,7 +1967,7 @@
       </c>
       <c r="J9" s="59" t="inlineStr">
         <is>
-          <t>10/16 착수 킥오프 회의에서 국·영문 혼용 번역 심의는 포함하고 인물 얼굴/딥페이크·해외법은 제외하기로 공식 합의</t>
+          <t>10/16 착수 킥오프 회의에서 국·영문 혼용 번역 검증은 포함하고 3D 솔리드 모델링·해외법은 제외하기로 공식 합의</t>
         </is>
       </c>
     </row>
@@ -1984,12 +1984,12 @@
       </c>
       <c r="C10" s="134" t="inlineStr">
         <is>
-          <t>긴 상세페이지(JPG) 세로 분할 시 문맥 단절 방지</t>
+          <t>다단 기술시방서(PDF/TIFF) 세로 분할 시 문맥 단절 방지</t>
         </is>
       </c>
       <c r="D10" s="134" t="inlineStr">
         <is>
-          <t>이커머스 긴 통이미지 상세페이지를 단순 고정 길이로 자를 경우 텍스트가 가로질러 잘리는 현상 예방 필요</t>
+          <t>전자조달 다단 스캔 기술시방서를 단순 고정 길이로 자를 경우 텍스트가 가로질러 잘리는 현상 예방 필요</t>
         </is>
       </c>
       <c r="E10" s="136" t="inlineStr">
@@ -2036,12 +2036,12 @@
       </c>
       <c r="C11" s="134" t="inlineStr">
         <is>
-          <t>법령·처분사례 크롤링 시 변경 조항 지능형 비교(Diff)</t>
+          <t>법령·심결사례 크롤링 시 변경 조항 지능형 비교(Diff)</t>
         </is>
       </c>
       <c r="D11" s="134" t="inlineStr">
         <is>
-          <t>국가법령 및 식약처 처분사례 주기적 수집 시 전체 재임베딩 부하를 줄이고 개정 조항만 정확히 식별할 필요</t>
+          <t>국가법령 및 공정위·표준원 심결사례 주기적 수집 시 전체 재임베딩 부하를 줄이고 개정 조항만 정확히 식별할 필요</t>
         </is>
       </c>
       <c r="E11" s="136" t="inlineStr">
@@ -2093,7 +2093,7 @@
       </c>
       <c r="D12" s="135" t="inlineStr">
         <is>
-          <t>발주사 미출시 신제품 시안 문구가 외부 LLM 학습 데이터로 유출되지 않도록 보안 통제 필수</t>
+          <t>발주사 미출시 신제품 계약·도서 조항이 외부 LLM 학습 데이터로 유출되지 않도록 보안 통제 필수</t>
         </is>
       </c>
       <c r="E12" s="136" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="C13" s="134" t="inlineStr">
         <is>
-          <t>식약처 사후 소명 대비 심의 확정 데이터 불변성 보장</t>
+          <t>공정위·표준원 사후 소명 대비 검증 확정 데이터 불변성 보장</t>
         </is>
       </c>
       <c r="D13" s="135" t="inlineStr">
         <is>
-          <t>심의 완료 후 사후 감사 시 당시 시안·캡처장면·AI근거·RA의견의 위변조 방지 보존 체계 필요</t>
+          <t>검증 완료 후 사후 감사 시 당시 계약·도서·스냅샷장면·AI근거·QA의견의 위변조 방지 보존 체계 필요</t>
         </is>
       </c>
       <c r="E13" s="136" t="inlineStr">
@@ -2175,7 +2175,7 @@
       </c>
       <c r="J13" s="60" t="inlineStr">
         <is>
-          <t>review_history_immutable 테이블 UPDATE/DELETE 차단 트리거 및 SHA-256 해시 체인 설계 반영</t>
+          <t>verify_history_immutable 테이블 UPDATE/DELETE 차단 트리거 및 SHA-256 해시 체인 설계 반영</t>
         </is>
       </c>
     </row>
